--- a/output/lgbm_clf/03_model_tuning/tuning_log.xlsx
+++ b/output/lgbm_clf/03_model_tuning/tuning_log.xlsx
@@ -647,19 +647,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3844</v>
+        <v>-0.4793</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6565</v>
+        <v>0.6098</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5598</v>
+        <v>0.5876</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4811</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -689,31 +689,31 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.005346020250638483</v>
+        <v>0.01286420870935064</v>
       </c>
       <c r="R3" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="S3" t="n">
         <v>0.7000000000000001</v>
       </c>
-      <c r="S3" t="n">
-        <v>0.6000000000000001</v>
-      </c>
       <c r="T3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="U3" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
@@ -729,19 +729,19 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4737</v>
+        <v>-0.3655</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6026</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>0.5759</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5004</v>
+        <v>0.4858</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -771,31 +771,31 @@
         <v>2</v>
       </c>
       <c r="O4" t="n">
+        <v>38</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.01323209490085383</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="T4" t="n">
         <v>48</v>
       </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.01703465952654019</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="T4" t="n">
-        <v>30</v>
-      </c>
       <c r="U4" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
@@ -811,19 +811,19 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4243</v>
+        <v>-0.3003</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6165</v>
+        <v>0.7149</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5417</v>
+        <v>0.5235</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4991</v>
+        <v>0.4917</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -853,31 +853,31 @@
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00725609974217179</v>
+        <v>0.01988783819448136</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="U5" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
@@ -893,19 +893,19 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.4281</v>
+        <v>-0.3501</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6374</v>
+        <v>0.6787</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5556</v>
+        <v>0.5395</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5099</v>
+        <v>0.4893</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -935,13 +935,13 @@
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01801696223102869</v>
+        <v>0.01616910989658199</v>
       </c>
       <c r="R6" t="n">
         <v>0.5</v>
@@ -950,16 +950,16 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="U6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
@@ -975,19 +975,19 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.3986</v>
+        <v>-0.4302</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6393</v>
+        <v>0.6374</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5417</v>
+        <v>0.5577</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4962</v>
+        <v>0.5099</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1017,31 +1017,31 @@
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007064422851792122</v>
+        <v>0.006402496877767496</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="U7" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
@@ -1057,19 +1057,19 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.4776</v>
+        <v>-0.325</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6113</v>
+        <v>0.7113</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5876</v>
+        <v>0.5534</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5012</v>
+        <v>0.4829</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1099,115 +1099,115 @@
         <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008371963619350529</v>
+        <v>0.0161406586661583</v>
       </c>
       <c r="R8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S8" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="S8" t="n">
-        <v>0.8</v>
-      </c>
       <c r="T8" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="U8" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>第2轮</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>-0.4884</v>
-      </c>
-      <c r="D9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.5925</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.5790999999999999</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.5018</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="C9" t="n">
+        <v>-0.4836</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6016</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5029</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>gbdt</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>auc</t>
         </is>
       </c>
-      <c r="K9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>0.00840348518072984</v>
-      </c>
-      <c r="R9" s="2" t="n">
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>20</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01031457179718306</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="S9" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="T9" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>350</v>
-      </c>
-      <c r="X9" s="2" t="b">
+      <c r="T9" t="n">
+        <v>27</v>
+      </c>
+      <c r="U9" t="n">
+        <v>29</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>340</v>
+      </c>
+      <c r="X9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1221,19 +1221,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.4839</v>
+        <v>-0.3936</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6012</v>
+        <v>0.6219</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5823</v>
+        <v>0.5139</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5028</v>
+        <v>0.5016</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1263,31 +1263,31 @@
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01580112435130032</v>
+        <v>0.006940157324973437</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="T10" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="U10" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
@@ -1303,19 +1303,19 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3936</v>
+        <v>-0.366</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6665</v>
+        <v>0.7049</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5684</v>
+        <v>0.578</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4917</v>
+        <v>0.4929</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1345,31 +1345,31 @@
         <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01005345263899089</v>
+        <v>0.01094035962746015</v>
       </c>
       <c r="R11" t="n">
         <v>0.8</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="U11" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
@@ -1385,19 +1385,19 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.4592</v>
+        <v>-0.4836</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5873</v>
+        <v>0.6016</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5406</v>
+        <v>0.5823</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5059</v>
+        <v>0.5029</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1433,191 +1433,191 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.006093485506907689</v>
+        <v>0.01428684136552512</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="S12" t="n">
         <v>0.6000000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="U12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>330</v>
+        <v>410</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>第2轮</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C13" t="n">
-        <v>-0.3596</v>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.6815</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.4856</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>-0.4997</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.5800999999999999</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>gbdt</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>auc</t>
         </is>
       </c>
-      <c r="K13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>38</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.01123593599033908</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="K13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>0.01542764651938401</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S13" s="2" t="n">
         <v>0.7000000000000001</v>
       </c>
-      <c r="T13" t="n">
-        <v>39</v>
-      </c>
-      <c r="U13" t="n">
-        <v>28</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
+      <c r="T13" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="X13" t="b">
+      <c r="X13" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>第2轮</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>-0.4884</v>
-      </c>
-      <c r="D14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.5925</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.5790999999999999</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0.5018</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="C14" t="n">
+        <v>-0.4836</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6016</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5029</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>gbdt</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>auc</t>
         </is>
       </c>
-      <c r="K14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="2" t="n">
-        <v>0.01013085397113691</v>
-      </c>
-      <c r="R14" s="2" t="n">
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.0137313847489818</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="S14" s="2" t="n">
+      <c r="S14" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="T14" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="V14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2" t="n">
-        <v>320</v>
-      </c>
-      <c r="X14" s="2" t="b">
+      <c r="T14" t="n">
+        <v>13</v>
+      </c>
+      <c r="U14" t="n">
+        <v>34</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>430</v>
+      </c>
+      <c r="X14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1631,19 +1631,19 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.4836</v>
+        <v>-0.4525</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6016</v>
+        <v>0.5994</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5823</v>
+        <v>0.547</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5029</v>
+        <v>0.505</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1673,16 +1673,16 @@
         <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01888930377778776</v>
+        <v>0.01347678150115432</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S15" t="n">
         <v>0.6000000000000001</v>
@@ -1691,13 +1691,13 @@
         <v>36</v>
       </c>
       <c r="U15" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
@@ -1713,19 +1713,19 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3662</v>
+        <v>-0.4524</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7006</v>
+        <v>0.5994</v>
       </c>
       <c r="F16" t="n">
-        <v>0.578</v>
+        <v>0.547</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4888</v>
+        <v>0.5048</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1755,31 +1755,31 @@
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01468635300837123</v>
+        <v>0.0153554531293762</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S16" t="n">
         <v>0.6000000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="U16" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
@@ -1795,19 +1795,19 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.4056</v>
+        <v>-0.353</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6287</v>
+        <v>0.7032</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5331</v>
+        <v>0.5673</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5011</v>
+        <v>0.4889</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1837,31 +1837,31 @@
         <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01862508950737736</v>
+        <v>0.01212962045334278</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U17" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
@@ -1877,19 +1877,19 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.4749</v>
+        <v>-0.4302</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5663</v>
+        <v>0.6374</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5385</v>
+        <v>0.5577</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5028</v>
+        <v>0.5099</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1919,16 +1919,16 @@
         <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01435986704589533</v>
+        <v>0.0112569606700179</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="S18" t="n">
         <v>0.5</v>
@@ -1937,13 +1937,13 @@
         <v>39</v>
       </c>
       <c r="U18" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
@@ -1959,19 +1959,19 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.4758</v>
+        <v>-0.3471</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6048</v>
+        <v>0.6936</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5491</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4915</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2001,31 +2001,31 @@
         <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.006489482482368532</v>
+        <v>0.01871058422061782</v>
       </c>
       <c r="R19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="S19" t="n">
-        <v>0.8</v>
-      </c>
       <c r="T19" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="U19" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
@@ -2041,19 +2041,19 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.4701</v>
+        <v>-0.2768</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6165</v>
+        <v>0.7261</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5833</v>
+        <v>0.5118</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5033</v>
+        <v>0.4911</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2083,31 +2083,31 @@
         <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.006286113086759603</v>
+        <v>0.007532450862886494</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="T20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>420</v>
+        <v>490</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
@@ -2123,19 +2123,19 @@
         <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.428</v>
+        <v>-0.4984</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6046</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5566</v>
+        <v>0.6004</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5089</v>
+        <v>0.5026</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2165,31 +2165,31 @@
         <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="P21" t="n">
         <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.006163170086035325</v>
+        <v>0.01860297629675842</v>
       </c>
       <c r="R21" t="n">
         <v>0.5</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="U21" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
@@ -2205,19 +2205,19 @@
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.4737</v>
+        <v>-0.4432</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6026</v>
+        <v>0.6171</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5759</v>
+        <v>0.5556</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5004</v>
+        <v>0.5048</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2247,31 +2247,31 @@
         <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.01407890440753013</v>
+        <v>0.01900814299237197</v>
       </c>
       <c r="R22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S22" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="S22" t="n">
-        <v>0.8</v>
-      </c>
       <c r="T22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U22" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
